--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99250</v>
+        <v>99253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99253</v>
+        <v>99254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533694</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99254</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99267</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99282</v>
+        <v>99284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533694</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99284</v>
+        <v>99297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18255-2026 artfynd.xlsx
+++ b/artfynd/A 18255-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533694</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544251</v>
       </c>
       <c r="B3" t="n">
-        <v>99297</v>
+        <v>99299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136531605</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136533826</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136541423</v>
       </c>
       <c r="B6" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
